--- a/src/assets/datas/Sabaqtar_MB.xlsx
+++ b/src/assets/datas/Sabaqtar_MB.xlsx
@@ -802,7 +802,7 @@
     <t>src\assets\datas\texts\test.md</t>
   </si>
   <si>
-    <t>src\assets\datas\pdfs\Test.pdf</t>
+    <t>/pdfs/Test.pdf</t>
   </si>
 </sst>
 </file>

--- a/src/assets/datas/Sabaqtar_MB.xlsx
+++ b/src/assets/datas/Sabaqtar_MB.xlsx
@@ -5,28 +5,27 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dev\kazakh-literature-portal\src\assets\datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\kazakh-literature-portal\src\assets\datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8808" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8808" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="📋 Нұсқаулық" sheetId="1" r:id="rId1"/>
     <sheet name="🎬 Видео сабақтар" sheetId="2" r:id="rId2"/>
-    <sheet name="📄 Конспекттер" sheetId="3" r:id="rId3"/>
-    <sheet name="📑 PDF материалдар" sheetId="4" r:id="rId4"/>
-    <sheet name="📊 Нәтиже" sheetId="5" r:id="rId5"/>
-    <sheet name="📚 Тараулар" sheetId="6" r:id="rId6"/>
-    <sheet name="📎 Материалдар" sheetId="7" r:id="rId7"/>
-    <sheet name="💬 Пікірлер" sheetId="8" r:id="rId8"/>
+    <sheet name="📑 PDF материалдар" sheetId="4" r:id="rId3"/>
+    <sheet name="📊 Нәтиже" sheetId="5" r:id="rId4"/>
+    <sheet name="📚 Тараулар" sheetId="6" r:id="rId5"/>
+    <sheet name="📎 Материалдар" sheetId="7" r:id="rId6"/>
+    <sheet name="💬 Пікірлер" sheetId="8" r:id="rId7"/>
   </sheets>
   <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="238">
   <si>
     <t>САБАҚТАР МӘЛІМЕТТЕР БАЗАСЫ — НҰСҚАУЛЫҚ</t>
   </si>
@@ -283,78 +282,18 @@
     <t>Жанр, стиль, тақырып, идея — әдебиеттану ғылымының іргелі ұғымдары.</t>
   </si>
   <si>
-    <t>📄 МӘТІНДІК КОНСПЕКТТЕР</t>
-  </si>
-  <si>
-    <t>Файл жолы: /texts/файл.md немесе /texts/файл.html  |  Немесе Markdown мәтін тікелей 'Мазмұн' бағанында</t>
-  </si>
-  <si>
-    <t>Конспект атауы</t>
-  </si>
-  <si>
     <t>Автор</t>
   </si>
   <si>
-    <t>Файл жолы (/texts/...) немесе URL</t>
-  </si>
-  <si>
-    <t>Оқу уақыты</t>
-  </si>
-  <si>
-    <t>Қысқаша мазмұны</t>
-  </si>
-  <si>
-    <t>Мұқағали Мақатаев лирикасының ерекшеліктері</t>
-  </si>
-  <si>
-    <t>25 мин</t>
-  </si>
-  <si>
-    <t>Ақынның поэтикалық тілі, образ жүйесі және лирикалық кейіпкері.</t>
-  </si>
-  <si>
-    <t>Абайдың қарасөздері — мазмұны мен маңызы</t>
-  </si>
-  <si>
-    <t>/texts/abai-karasoz.md</t>
-  </si>
-  <si>
-    <t>20 мин</t>
-  </si>
-  <si>
-    <t>38 қарасөздің мазмұны, тақырыптары мен философиялық маңызы.</t>
-  </si>
-  <si>
-    <t>/texts/literature-theory.md</t>
-  </si>
-  <si>
-    <t>15 мин</t>
-  </si>
-  <si>
-    <t>Жанр, стиль, тақырып, идея, кейіпкер — негізгі терминдер.</t>
-  </si>
-  <si>
-    <t>Заманауи қазақ прозасы: тенденциялар</t>
-  </si>
-  <si>
     <t>Дина Сәрсенова</t>
   </si>
   <si>
-    <t>/texts/modern-prose.md</t>
-  </si>
-  <si>
     <t>https://images.unsplash.com/photo-1513475382585-d06e58bcb0e0?w=600&amp;q=80</t>
   </si>
   <si>
-    <t>30 мин</t>
-  </si>
-  <si>
     <t>Проза</t>
   </si>
   <si>
-    <t>2000–2024 жылдардағы прозалық туындылардың тенденциялары.</t>
-  </si>
-  <si>
     <t>📑 PDF МАТЕРИАЛДАР</t>
   </si>
   <si>
@@ -797,9 +736,6 @@
   </si>
   <si>
     <t>PDF материал ғылыми деңгейде, бірақ студенттерге кейде қиын болуы мүмкін.</t>
-  </si>
-  <si>
-    <t>src\assets\datas\texts\test.md</t>
   </si>
   <si>
     <t>/pdfs/Test.pdf</t>
@@ -809,7 +745,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -850,12 +786,6 @@
       <b/>
       <sz val="9"/>
       <color rgb="FF8B3A1E"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color rgb="FF3A5C3A"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -951,7 +881,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -971,25 +901,22 @@
     <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1333,28 +1260,28 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:5" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
     </row>
     <row r="3" spans="1:5" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="19" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
+      <c r="B3" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
     </row>
     <row r="5" spans="1:5" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="16" t="s">
+      <c r="B5" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="17"/>
-      <c r="D5" s="17"/>
-      <c r="E5" s="17"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
     </row>
     <row r="6" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1"/>
@@ -1405,12 +1332,12 @@
       </c>
     </row>
     <row r="11" spans="1:5" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="18" t="s">
+      <c r="B11" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="17"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="17"/>
+      <c r="C11" s="16"/>
+      <c r="D11" s="16"/>
+      <c r="E11" s="16"/>
     </row>
     <row r="12" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
@@ -1489,32 +1416,32 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:11" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
-      <c r="H2" s="17"/>
-      <c r="I2" s="17"/>
-      <c r="J2" s="17"/>
-      <c r="K2" s="17"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="16"/>
+      <c r="J2" s="16"/>
+      <c r="K2" s="16"/>
     </row>
     <row r="3" spans="1:11" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="17"/>
-      <c r="G3" s="17"/>
-      <c r="H3" s="17"/>
-      <c r="I3" s="17"/>
-      <c r="J3" s="17"/>
-      <c r="K3" s="17"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16"/>
+      <c r="H3" s="16"/>
+      <c r="I3" s="16"/>
+      <c r="J3" s="16"/>
+      <c r="K3" s="16"/>
     </row>
     <row r="5" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3"/>
@@ -1817,7 +1744,7 @@
     <col min="4" max="4" width="28" customWidth="1"/>
     <col min="5" max="5" width="38" customWidth="1"/>
     <col min="6" max="6" width="28" customWidth="1"/>
-    <col min="7" max="7" width="16" customWidth="1"/>
+    <col min="7" max="7" width="14" customWidth="1"/>
     <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="10" width="18" customWidth="1"/>
     <col min="11" max="11" width="30" customWidth="1"/>
@@ -1825,63 +1752,63 @@
   <sheetData>
     <row r="2" spans="1:11" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="22" t="s">
+        <v>89</v>
+      </c>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="16"/>
+      <c r="J2" s="16"/>
+      <c r="K2" s="16"/>
+    </row>
+    <row r="3" spans="1:11" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="18" t="s">
+        <v>90</v>
+      </c>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16"/>
+      <c r="H3" s="16"/>
+      <c r="I3" s="16"/>
+      <c r="J3" s="16"/>
+      <c r="K3" s="16"/>
+    </row>
+    <row r="5" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="7"/>
+      <c r="B5" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="D5" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
-      <c r="H2" s="17"/>
-      <c r="I2" s="17"/>
-      <c r="J2" s="17"/>
-      <c r="K2" s="17"/>
-    </row>
-    <row r="3" spans="1:11" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="19" t="s">
-        <v>86</v>
-      </c>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="17"/>
-      <c r="G3" s="17"/>
-      <c r="H3" s="17"/>
-      <c r="I3" s="17"/>
-      <c r="J3" s="17"/>
-      <c r="K3" s="17"/>
-    </row>
-    <row r="5" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="6"/>
-      <c r="B5" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="F5" s="6" t="s">
+      <c r="E5" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="F5" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="G5" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="H5" s="6" t="s">
+      <c r="G5" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="H5" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="I5" s="6" t="s">
+      <c r="I5" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="J5" s="6" t="s">
+      <c r="J5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="K5" s="6" t="s">
-        <v>91</v>
+      <c r="K5" s="7" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -1890,31 +1817,31 @@
         <v>1</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>257</v>
+        <v>66</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>237</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>47</v>
+        <v>71</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -1923,31 +1850,31 @@
         <v>2</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>96</v>
+        <v>86</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>100</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>43</v>
+        <v>87</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>46</v>
+        <v>88</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -1956,31 +1883,31 @@
         <v>3</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>78</v>
+        <v>103</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>99</v>
+        <v>58</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>104</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>81</v>
+        <v>60</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>83</v>
+        <v>62</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -1989,31 +1916,31 @@
         <v>4</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>104</v>
+        <v>79</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>108</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>63</v>
+        <v>83</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -2062,260 +1989,6 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:K11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="3" customWidth="1"/>
-    <col min="2" max="2" width="5" customWidth="1"/>
-    <col min="3" max="3" width="35" customWidth="1"/>
-    <col min="4" max="4" width="28" customWidth="1"/>
-    <col min="5" max="5" width="38" customWidth="1"/>
-    <col min="6" max="6" width="28" customWidth="1"/>
-    <col min="7" max="7" width="14" customWidth="1"/>
-    <col min="8" max="8" width="12" customWidth="1"/>
-    <col min="9" max="10" width="18" customWidth="1"/>
-    <col min="11" max="11" width="30" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="1:11" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="23" t="s">
-        <v>109</v>
-      </c>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
-      <c r="H2" s="17"/>
-      <c r="I2" s="17"/>
-      <c r="J2" s="17"/>
-      <c r="K2" s="17"/>
-    </row>
-    <row r="3" spans="1:11" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="19" t="s">
-        <v>110</v>
-      </c>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="17"/>
-      <c r="G3" s="17"/>
-      <c r="H3" s="17"/>
-      <c r="I3" s="17"/>
-      <c r="J3" s="17"/>
-      <c r="K3" s="17"/>
-    </row>
-    <row r="5" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="8"/>
-      <c r="B5" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>111</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="G5" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="H5" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="I5" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="J5" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="K5" s="8" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="4"/>
-      <c r="B6" s="4">
-        <v>1</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>258</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="J6" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="K6" s="4" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2">
-        <v>2</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="4"/>
-      <c r="B8" s="4">
-        <v>3</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="I8" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="J8" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="K8" s="4" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2">
-        <v>4</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>128</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="4"/>
-      <c r="B10" s="4">
-        <v>5</v>
-      </c>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
-      <c r="I10" s="4"/>
-      <c r="J10" s="4"/>
-      <c r="K10" s="4"/>
-    </row>
-    <row r="11" spans="1:11" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2">
-        <v>6</v>
-      </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="B3:K3"/>
-    <mergeCell ref="B2:K2"/>
-  </mergeCells>
-  <dataValidations count="1">
-    <dataValidation type="list" sqref="H6:H500">
-      <formula1>"Оңай,Орташа,Жоғары"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A2:F8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -2326,115 +1999,115 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="20" t="s">
-        <v>132</v>
-      </c>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
+      <c r="B2" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
     </row>
     <row r="4" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="10"/>
-      <c r="B4" s="10" t="s">
-        <v>133</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>134</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>135</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>136</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>137</v>
+      <c r="A4" s="9"/>
+      <c r="B4" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="12">
+      <c r="C5" s="11">
         <f>COUNTA('🎬 Видео сабақтар'!C6:C500)</f>
         <v>6</v>
       </c>
-      <c r="D5" s="12">
+      <c r="D5" s="11">
         <f>COUNTA('🎬 Видео сабақтар'!D6:D500)</f>
         <v>6</v>
       </c>
-      <c r="E5" s="12">
+      <c r="E5" s="11">
         <f>C5-D5</f>
         <v>0</v>
       </c>
-      <c r="F5" s="12">
+      <c r="F5" s="11">
         <f>COUNTA('🎬 Видео сабақтар'!E6:E500)</f>
         <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="13" t="s">
+      <c r="B6" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="14">
-        <f>COUNTA('📄 Конспекттер'!C6:C500)</f>
-        <v>4</v>
-      </c>
-      <c r="D6" s="14">
-        <f>COUNTA('📄 Конспекттер'!D6:D500)</f>
-        <v>4</v>
-      </c>
-      <c r="E6" s="14">
+      <c r="C6" s="13">
+        <f>COUNTA(#REF!)</f>
+        <v>1</v>
+      </c>
+      <c r="D6" s="13">
+        <f>COUNTA(#REF!)</f>
+        <v>1</v>
+      </c>
+      <c r="E6" s="13">
         <f>C6-D6</f>
         <v>0</v>
       </c>
-      <c r="F6" s="14">
-        <f>COUNTA('📄 Конспекттер'!E6:E500)</f>
-        <v>4</v>
+      <c r="F6" s="13">
+        <f>COUNTA(#REF!)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="C7" s="12">
+      <c r="C7" s="11">
         <f>COUNTA('📑 PDF материалдар'!C6:C500)</f>
         <v>4</v>
       </c>
-      <c r="D7" s="12">
+      <c r="D7" s="11">
         <f>COUNTA('📑 PDF материалдар'!D6:D500)</f>
         <v>4</v>
       </c>
-      <c r="E7" s="12">
+      <c r="E7" s="11">
         <f>C7-D7</f>
         <v>0</v>
       </c>
-      <c r="F7" s="12">
+      <c r="F7" s="11">
         <f>COUNTA('📑 PDF материалдар'!E6:E500)</f>
         <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="15"/>
-      <c r="B8" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="C8" s="15">
+      <c r="A8" s="14"/>
+      <c r="B8" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="C8" s="14">
         <f>SUM(C5:C7)</f>
-        <v>14</v>
-      </c>
-      <c r="D8" s="15">
+        <v>11</v>
+      </c>
+      <c r="D8" s="14">
         <f>SUM(D5:D7)</f>
-        <v>14</v>
-      </c>
-      <c r="E8" s="15">
+        <v>11</v>
+      </c>
+      <c r="E8" s="14">
         <f>SUM(E5:E7)</f>
         <v>0</v>
       </c>
-      <c r="F8" s="15">
+      <c r="F8" s="14">
         <f>SUM(F5:F7)</f>
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -2445,7 +2118,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A2:H20"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2459,49 +2132,49 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="20" t="s">
-        <v>139</v>
-      </c>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
-      <c r="H2" s="17"/>
+      <c r="B2" s="19" t="s">
+        <v>119</v>
+      </c>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
     </row>
     <row r="3" spans="1:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="19" t="s">
-        <v>140</v>
-      </c>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="17"/>
-      <c r="G3" s="17"/>
-      <c r="H3" s="17"/>
+      <c r="B3" s="18" t="s">
+        <v>120</v>
+      </c>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16"/>
+      <c r="H3" s="16"/>
     </row>
     <row r="5" spans="1:8" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="10"/>
-      <c r="B5" s="10" t="s">
-        <v>141</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>142</v>
-      </c>
-      <c r="D5" s="10" t="s">
-        <v>143</v>
-      </c>
-      <c r="E5" s="10" t="s">
-        <v>144</v>
-      </c>
-      <c r="F5" s="10" t="s">
-        <v>145</v>
-      </c>
-      <c r="G5" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="H5" s="10" t="s">
-        <v>147</v>
+      <c r="A5" s="9"/>
+      <c r="B5" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2510,16 +2183,16 @@
         <v>1</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>148</v>
+        <v>128</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>149</v>
+        <v>129</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>151</v>
+        <v>131</v>
       </c>
       <c r="G6" s="4"/>
       <c r="H6" s="4">
@@ -2532,16 +2205,16 @@
         <v>1</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>148</v>
+        <v>128</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>152</v>
+        <v>132</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>153</v>
+        <v>133</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>154</v>
+        <v>134</v>
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="2">
@@ -2554,16 +2227,16 @@
         <v>1</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>148</v>
+        <v>128</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>155</v>
+        <v>135</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>156</v>
+        <v>136</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>157</v>
+        <v>137</v>
       </c>
       <c r="G8" s="4"/>
       <c r="H8" s="4">
@@ -2576,16 +2249,16 @@
         <v>1</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>148</v>
+        <v>128</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>158</v>
+        <v>138</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>159</v>
+        <v>139</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="G9" s="2"/>
       <c r="H9" s="2">
@@ -2598,16 +2271,16 @@
         <v>1</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>148</v>
+        <v>128</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>161</v>
+        <v>141</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>162</v>
+        <v>142</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>163</v>
+        <v>143</v>
       </c>
       <c r="G10" s="4"/>
       <c r="H10" s="4">
@@ -2620,16 +2293,16 @@
         <v>2</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>148</v>
+        <v>128</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>164</v>
+        <v>144</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>165</v>
+        <v>145</v>
       </c>
       <c r="G11" s="2"/>
       <c r="H11" s="2">
@@ -2642,16 +2315,16 @@
         <v>2</v>
       </c>
       <c r="C12" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="F12" s="4" t="s">
         <v>148</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>168</v>
       </c>
       <c r="G12" s="4"/>
       <c r="H12" s="4">
@@ -2664,16 +2337,16 @@
         <v>2</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>148</v>
+        <v>128</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>169</v>
+        <v>149</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>171</v>
+        <v>151</v>
       </c>
       <c r="G13" s="2"/>
       <c r="H13" s="2">
@@ -2686,16 +2359,16 @@
         <v>1</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>172</v>
+        <v>152</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>173</v>
+        <v>153</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>174</v>
+        <v>154</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>175</v>
+        <v>155</v>
       </c>
       <c r="G14" s="4"/>
       <c r="H14" s="4">
@@ -2708,16 +2381,16 @@
         <v>1</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>172</v>
+        <v>152</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>176</v>
+        <v>156</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>177</v>
+        <v>157</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>178</v>
+        <v>158</v>
       </c>
       <c r="G15" s="2"/>
       <c r="H15" s="2">
@@ -2730,16 +2403,16 @@
         <v>1</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>172</v>
+        <v>152</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>179</v>
+        <v>159</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>181</v>
+        <v>161</v>
       </c>
       <c r="G16" s="4"/>
       <c r="H16" s="4">
@@ -2752,16 +2425,16 @@
         <v>1</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>172</v>
+        <v>152</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>182</v>
+        <v>162</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>183</v>
+        <v>163</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>184</v>
+        <v>164</v>
       </c>
       <c r="G17" s="2"/>
       <c r="H17" s="2">
@@ -2774,16 +2447,16 @@
         <v>1</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>186</v>
+        <v>166</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>187</v>
+        <v>167</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>188</v>
+        <v>168</v>
       </c>
       <c r="G18" s="4"/>
       <c r="H18" s="4">
@@ -2796,16 +2469,16 @@
         <v>1</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>191</v>
+        <v>171</v>
       </c>
       <c r="G19" s="2"/>
       <c r="H19" s="2">
@@ -2818,16 +2491,16 @@
         <v>1</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>192</v>
+        <v>172</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>193</v>
+        <v>173</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>194</v>
+        <v>174</v>
       </c>
       <c r="G20" s="4"/>
       <c r="H20" s="4">
@@ -2843,7 +2516,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A2:H15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2858,49 +2531,49 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="21" t="s">
-        <v>195</v>
-      </c>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
-      <c r="H2" s="17"/>
+      <c r="B2" s="20" t="s">
+        <v>175</v>
+      </c>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
     </row>
     <row r="3" spans="1:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="19" t="s">
-        <v>196</v>
-      </c>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="17"/>
-      <c r="G3" s="17"/>
-      <c r="H3" s="17"/>
+      <c r="B3" s="18" t="s">
+        <v>176</v>
+      </c>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16"/>
+      <c r="H3" s="16"/>
     </row>
     <row r="5" spans="1:8" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3"/>
       <c r="B5" s="3" t="s">
-        <v>141</v>
+        <v>121</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>142</v>
+        <v>122</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>111</v>
+        <v>91</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>197</v>
+        <v>177</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>198</v>
+        <v>178</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>199</v>
+        <v>179</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>147</v>
+        <v>127</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2909,19 +2582,19 @@
         <v>1</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>148</v>
+        <v>128</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>201</v>
+        <v>181</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>202</v>
+        <v>182</v>
       </c>
       <c r="H6" s="4">
         <v>1</v>
@@ -2933,19 +2606,19 @@
         <v>1</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>148</v>
+        <v>128</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>204</v>
+        <v>184</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>205</v>
+        <v>185</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="H7" s="2">
         <v>2</v>
@@ -2957,19 +2630,19 @@
         <v>1</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>148</v>
+        <v>128</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>208</v>
+        <v>188</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>209</v>
+        <v>189</v>
       </c>
       <c r="H8" s="4">
         <v>3</v>
@@ -2981,19 +2654,19 @@
         <v>1</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>148</v>
+        <v>128</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>211</v>
+        <v>191</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>212</v>
+        <v>192</v>
       </c>
       <c r="H9" s="2">
         <v>4</v>
@@ -3005,19 +2678,19 @@
         <v>2</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>148</v>
+        <v>128</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>213</v>
+        <v>193</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>214</v>
+        <v>194</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>215</v>
+        <v>195</v>
       </c>
       <c r="H10" s="4">
         <v>1</v>
@@ -3029,19 +2702,19 @@
         <v>2</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>148</v>
+        <v>128</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>216</v>
+        <v>196</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>217</v>
+        <v>197</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>218</v>
+        <v>198</v>
       </c>
       <c r="H11" s="2">
         <v>2</v>
@@ -3053,19 +2726,19 @@
         <v>1</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>172</v>
+        <v>152</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>219</v>
+        <v>199</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>221</v>
+        <v>201</v>
       </c>
       <c r="H12" s="4">
         <v>1</v>
@@ -3077,19 +2750,19 @@
         <v>1</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>172</v>
+        <v>152</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>222</v>
+        <v>202</v>
       </c>
       <c r="E13" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="G13" s="2" t="s">
         <v>204</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>224</v>
       </c>
       <c r="H13" s="2">
         <v>2</v>
@@ -3101,19 +2774,19 @@
         <v>1</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>226</v>
+        <v>206</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>116</v>
+        <v>96</v>
       </c>
       <c r="H14" s="4">
         <v>1</v>
@@ -3125,19 +2798,19 @@
         <v>1</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>227</v>
+        <v>207</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>204</v>
+        <v>184</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>228</v>
+        <v>208</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>229</v>
+        <v>209</v>
       </c>
       <c r="H15" s="2">
         <v>2</v>
@@ -3152,7 +2825,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A2:H12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -3167,49 +2840,49 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="22" t="s">
-        <v>230</v>
-      </c>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
-      <c r="H2" s="17"/>
+      <c r="B2" s="21" t="s">
+        <v>210</v>
+      </c>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
     </row>
     <row r="3" spans="1:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="19" t="s">
-        <v>231</v>
-      </c>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="17"/>
-      <c r="G3" s="17"/>
-      <c r="H3" s="17"/>
+      <c r="B3" s="18" t="s">
+        <v>211</v>
+      </c>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16"/>
+      <c r="H3" s="16"/>
     </row>
     <row r="5" spans="1:8" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="6"/>
       <c r="B5" s="6" t="s">
-        <v>141</v>
+        <v>121</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>142</v>
+        <v>122</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>232</v>
+        <v>212</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>233</v>
+        <v>213</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>234</v>
+        <v>214</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>235</v>
+        <v>215</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>147</v>
+        <v>127</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3218,19 +2891,19 @@
         <v>1</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>148</v>
+        <v>128</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>236</v>
+        <v>216</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>237</v>
+        <v>217</v>
       </c>
       <c r="F6" s="4">
         <v>5</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>238</v>
+        <v>218</v>
       </c>
       <c r="H6" s="4">
         <v>1</v>
@@ -3242,19 +2915,19 @@
         <v>1</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>148</v>
+        <v>128</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>239</v>
+        <v>219</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="F7" s="2">
         <v>5</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>241</v>
+        <v>221</v>
       </c>
       <c r="H7" s="2">
         <v>2</v>
@@ -3266,19 +2939,19 @@
         <v>1</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>148</v>
+        <v>128</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>242</v>
+        <v>222</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>243</v>
+        <v>223</v>
       </c>
       <c r="F8" s="4">
         <v>4</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>244</v>
+        <v>224</v>
       </c>
       <c r="H8" s="4">
         <v>3</v>
@@ -3290,19 +2963,19 @@
         <v>2</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>148</v>
+        <v>128</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>245</v>
+        <v>225</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>246</v>
+        <v>226</v>
       </c>
       <c r="F9" s="2">
         <v>5</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>247</v>
+        <v>227</v>
       </c>
       <c r="H9" s="2">
         <v>1</v>
@@ -3314,19 +2987,19 @@
         <v>2</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>148</v>
+        <v>128</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>248</v>
+        <v>228</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>249</v>
+        <v>229</v>
       </c>
       <c r="F10" s="4">
         <v>4</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="H10" s="4">
         <v>2</v>
@@ -3338,19 +3011,19 @@
         <v>1</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>172</v>
+        <v>152</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>251</v>
+        <v>231</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>252</v>
+        <v>232</v>
       </c>
       <c r="F11" s="2">
         <v>5</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>253</v>
+        <v>233</v>
       </c>
       <c r="H11" s="2">
         <v>1</v>
@@ -3362,19 +3035,19 @@
         <v>1</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>254</v>
+        <v>234</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>255</v>
+        <v>235</v>
       </c>
       <c r="F12" s="4">
         <v>4</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>256</v>
+        <v>236</v>
       </c>
       <c r="H12" s="4">
         <v>1</v>

--- a/src/assets/datas/Sabaqtar_MB.xlsx
+++ b/src/assets/datas/Sabaqtar_MB.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8808" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8808" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="📋 Нұсқаулық" sheetId="1" r:id="rId1"/>
@@ -180,9 +180,6 @@
     <t>Берік Әшімов</t>
   </si>
   <si>
-    <t>/videos/muqagali-lirika.mp4</t>
-  </si>
-  <si>
     <t>https://images.unsplash.com/photo-1455390582262-044cdead277a?w=600&amp;q=80</t>
   </si>
   <si>
@@ -739,6 +736,9 @@
   </si>
   <si>
     <t>/pdfs/Test.pdf</t>
+  </si>
+  <si>
+    <t>/videos/Test.mp4</t>
   </si>
 </sst>
 </file>
@@ -758,47 +758,63 @@
       <sz val="13"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
     <font>
       <i/>
       <sz val="9"/>
       <color rgb="FF9A8A72"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF1A1208"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <color rgb="FF8B3A1E"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <color rgb="FF2A3A5C"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <color rgb="FF1A1208"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
   </fonts>
   <fills count="11">
@@ -941,10 +957,10 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1521,25 +1537,25 @@
         <v>50</v>
       </c>
       <c r="E7" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="G7" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="H7" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="H7" s="2" t="s">
+      <c r="I7" s="2" t="s">
         <v>54</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>55</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>47</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -1548,31 +1564,31 @@
         <v>3</v>
       </c>
       <c r="C8" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D8" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="E8" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="F8" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="G8" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="H8" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="I8" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="H8" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="I8" s="4" t="s">
+      <c r="J8" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="J8" s="4" t="s">
+      <c r="K8" s="4" t="s">
         <v>63</v>
-      </c>
-      <c r="K8" s="4" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -1581,31 +1597,31 @@
         <v>4</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="E9" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="F9" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="G9" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="G9" s="2" t="s">
+      <c r="H9" s="2" t="s">
         <v>69</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>70</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>46</v>
       </c>
       <c r="J9" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="K9" s="2" t="s">
         <v>71</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -1614,31 +1630,31 @@
         <v>5</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>41</v>
       </c>
       <c r="E10" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="F10" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="G10" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="G10" s="4" t="s">
-        <v>76</v>
-      </c>
       <c r="H10" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="I10" s="4" t="s">
         <v>54</v>
-      </c>
-      <c r="I10" s="4" t="s">
-        <v>55</v>
       </c>
       <c r="J10" s="4" t="s">
         <v>47</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -1647,31 +1663,31 @@
         <v>6</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="E11" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="F11" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="G11" s="2" t="s">
         <v>81</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>82</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>45</v>
       </c>
       <c r="I11" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="K11" s="2" t="s">
         <v>83</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -1751,8 +1767,8 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:11" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="22" t="s">
-        <v>89</v>
+      <c r="B2" s="21" t="s">
+        <v>88</v>
       </c>
       <c r="C2" s="16"/>
       <c r="D2" s="16"/>
@@ -1766,7 +1782,7 @@
     </row>
     <row r="3" spans="1:11" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="18" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C3" s="16"/>
       <c r="D3" s="16"/>
@@ -1784,19 +1800,19 @@
         <v>30</v>
       </c>
       <c r="C5" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="E5" s="7" t="s">
         <v>91</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>92</v>
       </c>
       <c r="F5" s="7" t="s">
         <v>34</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H5" s="7" t="s">
         <v>36</v>
@@ -1808,7 +1824,7 @@
         <v>38</v>
       </c>
       <c r="K5" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -1817,31 +1833,31 @@
         <v>1</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I6" s="4" t="s">
         <v>46</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -1850,31 +1866,31 @@
         <v>2</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E7" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="F7" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="G7" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="H7" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="I7" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="J7" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="K7" s="2" t="s">
         <v>101</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -1883,31 +1899,31 @@
         <v>3</v>
       </c>
       <c r="C8" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E8" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="D8" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="E8" s="8" t="s">
+      <c r="F8" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="G8" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="F8" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="G8" s="4" t="s">
+      <c r="H8" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="K8" s="4" t="s">
         <v>105</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="I8" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="J8" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="K8" s="4" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -1916,31 +1932,31 @@
         <v>4</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E9" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="E9" s="8" t="s">
+      <c r="F9" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="G9" s="2" t="s">
         <v>109</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>110</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>45</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -2000,7 +2016,7 @@
   <sheetData>
     <row r="2" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="19" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C2" s="16"/>
       <c r="D2" s="16"/>
@@ -2010,19 +2026,19 @@
     <row r="4" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="9"/>
       <c r="B4" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="C4" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="D4" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="E4" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="F4" s="9" t="s">
         <v>116</v>
-      </c>
-      <c r="F4" s="9" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -2091,7 +2107,7 @@
     <row r="8" spans="1:6" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="14"/>
       <c r="B8" s="14" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C8" s="14">
         <f>SUM(C5:C7)</f>
@@ -2133,7 +2149,7 @@
   <sheetData>
     <row r="2" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="19" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C2" s="16"/>
       <c r="D2" s="16"/>
@@ -2144,7 +2160,7 @@
     </row>
     <row r="3" spans="1:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="18" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C3" s="16"/>
       <c r="D3" s="16"/>
@@ -2156,25 +2172,25 @@
     <row r="5" spans="1:8" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="9"/>
       <c r="B5" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="C5" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="D5" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="E5" s="9" t="s">
         <v>123</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="F5" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="G5" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="G5" s="9" t="s">
+      <c r="H5" s="9" t="s">
         <v>126</v>
-      </c>
-      <c r="H5" s="9" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2183,16 +2199,16 @@
         <v>1</v>
       </c>
       <c r="C6" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="D6" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="E6" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="F6" s="4" t="s">
         <v>130</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>131</v>
       </c>
       <c r="G6" s="4"/>
       <c r="H6" s="4">
@@ -2205,16 +2221,16 @@
         <v>1</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D7" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
         <v>133</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>134</v>
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="2">
@@ -2227,16 +2243,16 @@
         <v>1</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D8" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="E8" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="F8" s="4" t="s">
         <v>136</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>137</v>
       </c>
       <c r="G8" s="4"/>
       <c r="H8" s="4">
@@ -2249,16 +2265,16 @@
         <v>1</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D9" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="F9" s="2" t="s">
         <v>139</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>140</v>
       </c>
       <c r="G9" s="2"/>
       <c r="H9" s="2">
@@ -2271,16 +2287,16 @@
         <v>1</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D10" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="E10" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="F10" s="4" t="s">
         <v>142</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>143</v>
       </c>
       <c r="G10" s="4"/>
       <c r="H10" s="4">
@@ -2293,16 +2309,16 @@
         <v>2</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D11" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F11" s="2" t="s">
         <v>144</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>145</v>
       </c>
       <c r="G11" s="2"/>
       <c r="H11" s="2">
@@ -2315,16 +2331,16 @@
         <v>2</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D12" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="E12" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="F12" s="4" t="s">
         <v>147</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>148</v>
       </c>
       <c r="G12" s="4"/>
       <c r="H12" s="4">
@@ -2337,16 +2353,16 @@
         <v>2</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D13" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="F13" s="2" t="s">
         <v>150</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>151</v>
       </c>
       <c r="G13" s="2"/>
       <c r="H13" s="2">
@@ -2359,16 +2375,16 @@
         <v>1</v>
       </c>
       <c r="C14" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="D14" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="E14" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="F14" s="4" t="s">
         <v>154</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>155</v>
       </c>
       <c r="G14" s="4"/>
       <c r="H14" s="4">
@@ -2381,16 +2397,16 @@
         <v>1</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D15" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="F15" s="2" t="s">
         <v>157</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>158</v>
       </c>
       <c r="G15" s="2"/>
       <c r="H15" s="2">
@@ -2403,16 +2419,16 @@
         <v>1</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D16" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="E16" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="F16" s="4" t="s">
         <v>160</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>161</v>
       </c>
       <c r="G16" s="4"/>
       <c r="H16" s="4">
@@ -2425,16 +2441,16 @@
         <v>1</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D17" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="E17" s="2" t="s">
+      <c r="F17" s="2" t="s">
         <v>163</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>164</v>
       </c>
       <c r="G17" s="2"/>
       <c r="H17" s="2">
@@ -2447,16 +2463,16 @@
         <v>1</v>
       </c>
       <c r="C18" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="D18" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="E18" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="E18" s="4" t="s">
+      <c r="F18" s="4" t="s">
         <v>167</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>168</v>
       </c>
       <c r="G18" s="4"/>
       <c r="H18" s="4">
@@ -2469,16 +2485,16 @@
         <v>1</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D19" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="E19" s="2" t="s">
+      <c r="F19" s="2" t="s">
         <v>170</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>171</v>
       </c>
       <c r="G19" s="2"/>
       <c r="H19" s="2">
@@ -2491,16 +2507,16 @@
         <v>1</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D20" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="E20" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="E20" s="4" t="s">
+      <c r="F20" s="4" t="s">
         <v>173</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>174</v>
       </c>
       <c r="G20" s="4"/>
       <c r="H20" s="4">
@@ -2532,7 +2548,7 @@
   <sheetData>
     <row r="2" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="20" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C2" s="16"/>
       <c r="D2" s="16"/>
@@ -2543,7 +2559,7 @@
     </row>
     <row r="3" spans="1:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="18" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C3" s="16"/>
       <c r="D3" s="16"/>
@@ -2555,25 +2571,25 @@
     <row r="5" spans="1:8" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3"/>
       <c r="B5" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>122</v>
-      </c>
       <c r="D5" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E5" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="G5" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>179</v>
-      </c>
       <c r="H5" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2582,19 +2598,19 @@
         <v>1</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D6" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="F6" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="E6" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="F6" s="4" t="s">
+      <c r="G6" s="4" t="s">
         <v>181</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>182</v>
       </c>
       <c r="H6" s="4">
         <v>1</v>
@@ -2606,19 +2622,19 @@
         <v>1</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D7" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="G7" s="2" t="s">
         <v>185</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>186</v>
       </c>
       <c r="H7" s="2">
         <v>2</v>
@@ -2630,19 +2646,19 @@
         <v>1</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D8" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="F8" s="4" t="s">
         <v>187</v>
       </c>
-      <c r="E8" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="F8" s="4" t="s">
+      <c r="G8" s="4" t="s">
         <v>188</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>189</v>
       </c>
       <c r="H8" s="4">
         <v>3</v>
@@ -2654,19 +2670,19 @@
         <v>1</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D9" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="F9" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="E9" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="F9" s="2" t="s">
+      <c r="G9" s="2" t="s">
         <v>191</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>192</v>
       </c>
       <c r="H9" s="2">
         <v>4</v>
@@ -2678,19 +2694,19 @@
         <v>2</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D10" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="F10" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="E10" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="F10" s="4" t="s">
+      <c r="G10" s="4" t="s">
         <v>194</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>195</v>
       </c>
       <c r="H10" s="4">
         <v>1</v>
@@ -2702,19 +2718,19 @@
         <v>2</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D11" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="F11" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="E11" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="F11" s="2" t="s">
+      <c r="G11" s="2" t="s">
         <v>197</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>198</v>
       </c>
       <c r="H11" s="2">
         <v>2</v>
@@ -2726,19 +2742,19 @@
         <v>1</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D12" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="F12" s="4" t="s">
         <v>199</v>
       </c>
-      <c r="E12" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="F12" s="4" t="s">
+      <c r="G12" s="4" t="s">
         <v>200</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>201</v>
       </c>
       <c r="H12" s="4">
         <v>1</v>
@@ -2750,19 +2766,19 @@
         <v>1</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D13" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="F13" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="E13" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="F13" s="2" t="s">
+      <c r="G13" s="2" t="s">
         <v>203</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>204</v>
       </c>
       <c r="H13" s="2">
         <v>2</v>
@@ -2774,19 +2790,19 @@
         <v>1</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D14" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="F14" s="4" t="s">
         <v>205</v>
       </c>
-      <c r="E14" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>206</v>
-      </c>
       <c r="G14" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H14" s="4">
         <v>1</v>
@@ -2798,19 +2814,19 @@
         <v>1</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D15" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="F15" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="E15" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="F15" s="2" t="s">
+      <c r="G15" s="2" t="s">
         <v>208</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>209</v>
       </c>
       <c r="H15" s="2">
         <v>2</v>
@@ -2840,8 +2856,8 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="21" t="s">
-        <v>210</v>
+      <c r="B2" s="22" t="s">
+        <v>209</v>
       </c>
       <c r="C2" s="16"/>
       <c r="D2" s="16"/>
@@ -2852,7 +2868,7 @@
     </row>
     <row r="3" spans="1:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="18" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C3" s="16"/>
       <c r="D3" s="16"/>
@@ -2864,25 +2880,25 @@
     <row r="5" spans="1:8" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="6"/>
       <c r="B5" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="C5" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="C5" s="6" t="s">
-        <v>122</v>
-      </c>
       <c r="D5" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="E5" s="6" t="s">
         <v>212</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="F5" s="6" t="s">
         <v>213</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="G5" s="6" t="s">
         <v>214</v>
       </c>
-      <c r="G5" s="6" t="s">
-        <v>215</v>
-      </c>
       <c r="H5" s="6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2891,19 +2907,19 @@
         <v>1</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D6" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="E6" s="4" t="s">
         <v>216</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>217</v>
       </c>
       <c r="F6" s="4">
         <v>5</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H6" s="4">
         <v>1</v>
@@ -2915,19 +2931,19 @@
         <v>1</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D7" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>219</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>220</v>
       </c>
       <c r="F7" s="2">
         <v>5</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H7" s="2">
         <v>2</v>
@@ -2939,19 +2955,19 @@
         <v>1</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D8" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="E8" s="4" t="s">
         <v>222</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>223</v>
       </c>
       <c r="F8" s="4">
         <v>4</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H8" s="4">
         <v>3</v>
@@ -2963,19 +2979,19 @@
         <v>2</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D9" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>225</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>226</v>
       </c>
       <c r="F9" s="2">
         <v>5</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H9" s="2">
         <v>1</v>
@@ -2987,19 +3003,19 @@
         <v>2</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D10" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="E10" s="4" t="s">
         <v>228</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>229</v>
       </c>
       <c r="F10" s="4">
         <v>4</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H10" s="4">
         <v>2</v>
@@ -3011,19 +3027,19 @@
         <v>1</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D11" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>231</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>232</v>
       </c>
       <c r="F11" s="2">
         <v>5</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H11" s="2">
         <v>1</v>
@@ -3035,19 +3051,19 @@
         <v>1</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D12" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="E12" s="4" t="s">
         <v>234</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>235</v>
       </c>
       <c r="F12" s="4">
         <v>4</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H12" s="4">
         <v>1</v>
